--- a/data/Material.xlsx
+++ b/data/Material.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\casa\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA43944A-8885-428D-9CA2-68D335404BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF217C40-0DA8-4487-918D-8E87A8DEFB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
+    <workbookView xWindow="20640" yWindow="2895" windowWidth="15765" windowHeight="11295" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="41">
   <si>
     <t>Arame Recozido</t>
   </si>
@@ -77,9 +77,6 @@
     <t>m²</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Ferro 3/8 CA-50</t>
   </si>
   <si>
@@ -141,6 +138,27 @@
   </si>
   <si>
     <t>Qnt</t>
+  </si>
+  <si>
+    <t>Flavio Pavel</t>
+  </si>
+  <si>
+    <t>Cidinha Olaria</t>
+  </si>
+  <si>
+    <t>Mercado Livre</t>
+  </si>
+  <si>
+    <t>Miranda</t>
+  </si>
+  <si>
+    <t>Robson</t>
+  </si>
+  <si>
+    <t>Categoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intermunicipal </t>
   </si>
 </sst>
 </file>
@@ -216,15 +234,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F73" totalsRowShown="0">
-  <autoFilter ref="A1:F73" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F84" totalsRowShown="0">
+  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3E150EE4-3582-4146-8DCA-704614BB6D6C}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{02D0EF72-3F92-4729-A04E-D1B299B7E2C7}" name="Und"/>
     <tableColumn id="3" xr3:uid="{E35A1F86-B51A-4135-8455-367B6BAD66B5}" name="Qnt" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{7CCF3AC5-2546-4A38-95A6-E04EC688DC34}" name="Local"/>
     <tableColumn id="5" xr3:uid="{0B1806D1-FED9-4573-88BD-38E411D4DB9B}" name="Valor Un" dataCellStyle="Moeda"/>
-    <tableColumn id="6" xr3:uid="{8EA2C009-E0CF-4C5C-B650-ACF37974B7E2}" name="Total" dataCellStyle="Moeda"/>
+    <tableColumn id="6" xr3:uid="{8EA2C009-E0CF-4C5C-B650-ACF37974B7E2}" name="Categoria" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -547,40 +565,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC58E5CE-1F21-4ED3-80F8-66E615B00334}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
         <v>32</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -589,18 +607,18 @@
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1">
         <v>62.25</v>
       </c>
-      <c r="F2" s="1">
-        <v>2988</v>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -609,18 +627,18 @@
         <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1">
         <v>40.6</v>
       </c>
-      <c r="F3" s="1">
-        <v>2517.2000000000003</v>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -629,18 +647,18 @@
         <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1">
         <v>13.5</v>
       </c>
-      <c r="F4" s="1">
-        <v>1080</v>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -649,13 +667,13 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1">
         <v>36.6</v>
       </c>
-      <c r="F5" s="1">
-        <v>366</v>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -669,13 +687,13 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="1">
-        <v>1000</v>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -689,13 +707,13 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1">
         <v>19</v>
       </c>
-      <c r="F7" s="1">
-        <v>475</v>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -709,18 +727,18 @@
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1">
         <v>19</v>
       </c>
-      <c r="F8" s="1">
-        <v>342</v>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -729,18 +747,18 @@
         <v>6800</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1">
         <v>1.51</v>
       </c>
-      <c r="F9" s="1">
-        <v>10268</v>
+      <c r="F9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -749,18 +767,18 @@
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1">
         <v>32.799999999999997</v>
       </c>
-      <c r="F10" s="1">
-        <v>2624</v>
+      <c r="F10" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -769,18 +787,18 @@
         <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1">
         <v>24.5</v>
       </c>
-      <c r="F11" s="1">
-        <v>1470</v>
+      <c r="F11" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -789,18 +807,18 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1">
         <v>20.7</v>
       </c>
-      <c r="F12" s="1">
-        <v>414</v>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -809,18 +827,18 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1">
         <v>20</v>
       </c>
-      <c r="F13" s="1">
-        <v>40</v>
+      <c r="F13" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -829,18 +847,18 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1">
         <v>290</v>
       </c>
-      <c r="F14" s="1">
-        <v>290</v>
+      <c r="F14" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
         <v>11</v>
@@ -849,18 +867,18 @@
         <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1">
         <v>50</v>
       </c>
-      <c r="F15" s="1">
-        <v>8250</v>
+      <c r="F15" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>11</v>
@@ -869,13 +887,13 @@
         <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="1">
         <v>19.2</v>
       </c>
-      <c r="F16" s="1">
-        <v>1920</v>
+      <c r="F16" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -889,13 +907,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1">
         <v>170</v>
       </c>
-      <c r="F17" s="1">
-        <v>2720</v>
+      <c r="F17" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -909,13 +927,13 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" s="1">
         <v>156</v>
       </c>
-      <c r="F18" s="1">
-        <v>1872</v>
+      <c r="F18" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,18 +947,18 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="1">
         <v>190</v>
       </c>
-      <c r="F19" s="1">
-        <v>2660</v>
+      <c r="F19" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
@@ -949,18 +967,18 @@
         <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="1">
         <v>88</v>
       </c>
-      <c r="F20" s="1">
-        <v>4224</v>
+      <c r="F20" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
         <v>6</v>
@@ -969,18 +987,18 @@
         <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" s="1">
         <v>51.59</v>
       </c>
-      <c r="F21" s="1">
-        <v>3198.5800000000004</v>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
@@ -989,18 +1007,18 @@
         <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" s="1">
         <v>16.5</v>
       </c>
-      <c r="F22" s="1">
-        <v>1320</v>
+      <c r="F22" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
@@ -1009,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E23" s="1">
         <v>52.69</v>
       </c>
-      <c r="F23" s="1">
-        <v>526.9</v>
+      <c r="F23" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1029,13 +1047,13 @@
         <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1">
         <v>23.65</v>
       </c>
-      <c r="F24" s="1">
-        <v>1182.5</v>
+      <c r="F24" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1049,13 +1067,13 @@
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1">
         <v>26.29</v>
       </c>
-      <c r="F25" s="1">
-        <v>657.25</v>
+      <c r="F25" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1069,18 +1087,18 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E26" s="1">
         <v>26.29</v>
       </c>
-      <c r="F26" s="1">
-        <v>473.21999999999997</v>
+      <c r="F26" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -1089,18 +1107,18 @@
         <v>6800</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1">
         <v>0.95</v>
       </c>
-      <c r="F27" s="1">
-        <v>6460</v>
+      <c r="F27" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1109,18 +1127,18 @@
         <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1">
         <v>51.4</v>
       </c>
-      <c r="F28" s="1">
-        <v>4112</v>
+      <c r="F28" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -1129,18 +1147,18 @@
         <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1">
         <v>39.71</v>
       </c>
-      <c r="F29" s="1">
-        <v>2382.6</v>
+      <c r="F29" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -1149,18 +1167,18 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E30" s="1">
         <v>20.9</v>
       </c>
-      <c r="F30" s="1">
-        <v>418</v>
+      <c r="F30" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -1169,18 +1187,18 @@
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" s="1">
         <v>70</v>
       </c>
-      <c r="F31" s="1">
-        <v>140</v>
+      <c r="F31" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -1189,18 +1207,18 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E32" s="1">
         <v>439.45</v>
       </c>
-      <c r="F32" s="1">
-        <v>439.45</v>
+      <c r="F32" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
@@ -1209,18 +1227,18 @@
         <v>165</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E33" s="1">
         <v>60.4</v>
       </c>
-      <c r="F33" s="1">
-        <v>9966</v>
+      <c r="F33" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -1229,13 +1247,13 @@
         <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1">
         <v>24.2</v>
       </c>
-      <c r="F34" s="1">
-        <v>2420</v>
+      <c r="F34" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1249,13 +1267,13 @@
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E35" s="1">
         <v>185</v>
       </c>
-      <c r="F35" s="1">
-        <v>2960</v>
+      <c r="F35" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1269,13 +1287,13 @@
         <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1">
         <v>165</v>
       </c>
-      <c r="F36" s="1">
-        <v>1980</v>
+      <c r="F36" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1289,18 +1307,18 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" s="1">
         <v>198</v>
       </c>
-      <c r="F37" s="1">
-        <v>2772</v>
+      <c r="F37" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -1309,18 +1327,18 @@
         <v>48</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E38" s="1">
         <v>63</v>
       </c>
-      <c r="F38" s="1">
-        <v>3024</v>
+      <c r="F38" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -1329,18 +1347,18 @@
         <v>62</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" s="1">
         <v>43</v>
       </c>
-      <c r="F39" s="1">
-        <v>2666</v>
+      <c r="F39" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -1349,18 +1367,18 @@
         <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E40" s="1">
         <v>14</v>
       </c>
-      <c r="F40" s="1">
-        <v>1120</v>
+      <c r="F40" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
@@ -1369,13 +1387,13 @@
         <v>10</v>
       </c>
       <c r="D41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E41" s="1">
         <v>52</v>
       </c>
-      <c r="F41" s="1">
-        <v>520</v>
+      <c r="F41" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,13 +1407,13 @@
         <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E42" s="1">
         <v>19.899999999999999</v>
       </c>
-      <c r="F42" s="1">
-        <v>994.99999999999989</v>
+      <c r="F42" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1409,13 +1427,13 @@
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E43" s="1">
         <v>19.899999999999999</v>
       </c>
-      <c r="F43" s="1">
-        <v>497.49999999999994</v>
+      <c r="F43" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1429,18 +1447,18 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E44" s="1">
         <v>19.899999999999999</v>
       </c>
-      <c r="F44" s="1">
-        <v>358.2</v>
+      <c r="F44" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
@@ -1449,18 +1467,18 @@
         <v>6800</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E45" s="1">
         <v>1.3</v>
       </c>
-      <c r="F45" s="1">
-        <v>8840</v>
+      <c r="F45" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
@@ -1469,18 +1487,18 @@
         <v>80</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E46" s="1">
         <v>39.9</v>
       </c>
-      <c r="F46" s="1">
-        <v>3192</v>
+      <c r="F46" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
@@ -1489,18 +1507,18 @@
         <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E47" s="1">
         <v>34</v>
       </c>
-      <c r="F47" s="1">
-        <v>2040</v>
+      <c r="F47" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
@@ -1509,18 +1527,18 @@
         <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E48" s="1">
         <v>19.899999999999999</v>
       </c>
-      <c r="F48" s="1">
-        <v>398</v>
+      <c r="F48" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
@@ -1529,18 +1547,18 @@
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E49" s="1">
         <v>179</v>
       </c>
-      <c r="F49" s="1">
-        <v>358</v>
+      <c r="F49" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -1549,18 +1567,18 @@
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E50" s="1">
         <v>329</v>
       </c>
-      <c r="F50" s="1">
-        <v>329</v>
+      <c r="F50" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
@@ -1569,18 +1587,18 @@
         <v>165</v>
       </c>
       <c r="D51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E51" s="1">
         <v>55.5</v>
       </c>
-      <c r="F51" s="1">
-        <v>9157.5</v>
+      <c r="F51" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
@@ -1589,13 +1607,13 @@
         <v>100</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E52" s="1">
         <v>18.899999999999999</v>
       </c>
-      <c r="F52" s="1">
-        <v>1889.9999999999998</v>
+      <c r="F52" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1609,13 +1627,13 @@
         <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E53" s="1">
         <v>159</v>
       </c>
-      <c r="F53" s="1">
-        <v>2544</v>
+      <c r="F53" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1629,13 +1647,13 @@
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E54" s="1">
         <v>140</v>
       </c>
-      <c r="F54" s="1">
-        <v>1680</v>
+      <c r="F54" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1649,18 +1667,18 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E55" s="1">
         <v>159</v>
       </c>
-      <c r="F55" s="1">
-        <v>2226</v>
+      <c r="F55" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
         <v>6</v>
@@ -1669,18 +1687,18 @@
         <v>48</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E56" s="1">
         <v>69.900000000000006</v>
       </c>
-      <c r="F56" s="1">
-        <v>3355.2000000000003</v>
+      <c r="F56" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
@@ -1689,18 +1707,18 @@
         <v>62</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E57" s="1">
         <v>49.9</v>
       </c>
-      <c r="F57" s="1">
-        <v>3093.7999999999997</v>
+      <c r="F57" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
@@ -1709,18 +1727,18 @@
         <v>80</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E58" s="1">
         <v>15.9</v>
       </c>
-      <c r="F58" s="1">
-        <v>1272</v>
+      <c r="F58" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B59" t="s">
         <v>7</v>
@@ -1729,13 +1747,13 @@
         <v>10</v>
       </c>
       <c r="D59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E59" s="1">
         <v>39.9</v>
       </c>
-      <c r="F59" s="1">
-        <v>399</v>
+      <c r="F59" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1749,13 +1767,13 @@
         <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E60" s="1">
         <v>18.899999999999999</v>
       </c>
-      <c r="F60" s="1">
-        <v>944.99999999999989</v>
+      <c r="F60" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1769,13 +1787,13 @@
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E61" s="1">
         <v>18.899999999999999</v>
       </c>
-      <c r="F61" s="1">
-        <v>472.49999999999994</v>
+      <c r="F61" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1789,18 +1807,18 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E62" s="1">
         <v>18.899999999999999</v>
       </c>
-      <c r="F62" s="1">
-        <v>340.2</v>
+      <c r="F62" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B63" t="s">
         <v>10</v>
@@ -1809,18 +1827,18 @@
         <v>6800</v>
       </c>
       <c r="D63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E63" s="1">
         <v>1.35</v>
       </c>
-      <c r="F63" s="1">
-        <v>9180</v>
+      <c r="F63" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
@@ -1829,18 +1847,18 @@
         <v>80</v>
       </c>
       <c r="D64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E64" s="1">
         <v>39.9</v>
       </c>
-      <c r="F64" s="1">
-        <v>3192</v>
+      <c r="F64" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B65" t="s">
         <v>10</v>
@@ -1849,18 +1867,18 @@
         <v>60</v>
       </c>
       <c r="D65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E65" s="1">
         <v>32.9</v>
       </c>
-      <c r="F65" s="1">
-        <v>1974</v>
+      <c r="F65" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
@@ -1869,18 +1887,18 @@
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E66" s="1">
         <v>19</v>
       </c>
-      <c r="F66" s="1">
-        <v>380</v>
+      <c r="F66" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B67" t="s">
         <v>10</v>
@@ -1889,18 +1907,18 @@
         <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E67" s="1">
         <v>359.9</v>
       </c>
-      <c r="F67" s="1">
-        <v>719.8</v>
+      <c r="F67" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B68" t="s">
         <v>10</v>
@@ -1909,18 +1927,18 @@
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E68" s="1">
         <v>119.9</v>
       </c>
-      <c r="F68" s="1">
-        <v>119.9</v>
+      <c r="F68" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
@@ -1929,18 +1947,18 @@
         <v>165</v>
       </c>
       <c r="D69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E69" s="1">
         <v>48.9</v>
       </c>
-      <c r="F69" s="1">
-        <v>8068.5</v>
+      <c r="F69" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
@@ -1949,13 +1967,13 @@
         <v>100</v>
       </c>
       <c r="D70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E70" s="1">
         <v>18.5</v>
       </c>
-      <c r="F70" s="1">
-        <v>1850</v>
+      <c r="F70" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -1969,13 +1987,13 @@
         <v>16</v>
       </c>
       <c r="D71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E71" s="1">
         <v>170</v>
       </c>
-      <c r="F71" s="1">
-        <v>2720</v>
+      <c r="F71" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1989,13 +2007,13 @@
         <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E72" s="1">
         <v>155</v>
       </c>
-      <c r="F72" s="1">
-        <v>1860</v>
+      <c r="F72" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2009,13 +2027,233 @@
         <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E73" s="1">
         <v>185</v>
       </c>
-      <c r="F73" s="1">
-        <v>2590</v>
+      <c r="F73" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2">
+        <v>48</v>
+      </c>
+      <c r="D74" t="s">
+        <v>37</v>
+      </c>
+      <c r="E74" s="1">
+        <v>54.5</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2">
+        <v>62</v>
+      </c>
+      <c r="D75" t="s">
+        <v>37</v>
+      </c>
+      <c r="E75" s="1">
+        <v>36.5</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>19</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2">
+        <v>80</v>
+      </c>
+      <c r="D76" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" s="1">
+        <v>11</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2">
+        <v>10</v>
+      </c>
+      <c r="D77" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="1">
+        <v>46</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="2">
+        <v>6800</v>
+      </c>
+      <c r="D78" t="s">
+        <v>34</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>26</v>
+      </c>
+      <c r="B79" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="2">
+        <v>2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>36</v>
+      </c>
+      <c r="E79" s="1">
+        <v>188.87</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80" s="1">
+        <v>283</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" s="2">
+        <v>16</v>
+      </c>
+      <c r="D81" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" s="1">
+        <v>110</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="2">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" s="1">
+        <v>110</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="2">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" s="1">
+        <v>118</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="2">
+        <v>6800</v>
+      </c>
+      <c r="D84" t="s">
+        <v>35</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/Material.xlsx
+++ b/data/Material.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\casa\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\orcamentos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF217C40-0DA8-4487-918D-8E87A8DEFB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E60A89C-4BE6-4247-82D6-D7B003733047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20640" yWindow="2895" windowWidth="15765" windowHeight="11295" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="42">
   <si>
     <t>Arame Recozido</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t xml:space="preserve">Intermunicipal </t>
+  </si>
+  <si>
+    <t>Quero-Quero</t>
   </si>
 </sst>
 </file>
@@ -234,8 +237,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F84" totalsRowShown="0">
-  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F85" totalsRowShown="0">
+  <autoFilter ref="A1:F85" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3E150EE4-3582-4146-8DCA-704614BB6D6C}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{02D0EF72-3F92-4729-A04E-D1B299B7E2C7}" name="Und"/>
@@ -565,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC58E5CE-1F21-4ED3-80F8-66E615B00334}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
@@ -2256,6 +2259,26 @@
         <v>40</v>
       </c>
     </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="2">
+        <v>165</v>
+      </c>
+      <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85" s="1">
+        <v>36</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Material.xlsx
+++ b/data/Material.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\orcamentos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E60A89C-4BE6-4247-82D6-D7B003733047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FF54AC-74B4-444F-9B86-88B562D354CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20640" yWindow="2895" windowWidth="15765" windowHeight="11295" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="41">
   <si>
     <t>Arame Recozido</t>
   </si>
@@ -159,9 +159,6 @@
   </si>
   <si>
     <t xml:space="preserve">Intermunicipal </t>
-  </si>
-  <si>
-    <t>Quero-Quero</t>
   </si>
 </sst>
 </file>
@@ -237,8 +234,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F85" totalsRowShown="0">
-  <autoFilter ref="A1:F85" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F84" totalsRowShown="0">
+  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3E150EE4-3582-4146-8DCA-704614BB6D6C}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{02D0EF72-3F92-4729-A04E-D1B299B7E2C7}" name="Und"/>
@@ -568,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC58E5CE-1F21-4ED3-80F8-66E615B00334}">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
@@ -833,7 +830,7 @@
         <v>17</v>
       </c>
       <c r="E13" s="1">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>18</v>
@@ -1193,7 +1190,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="1">
-        <v>70</v>
+        <v>315</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>18</v>
@@ -2257,26 +2254,6 @@
       </c>
       <c r="F84" s="1" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>24</v>
-      </c>
-      <c r="B85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="2">
-        <v>165</v>
-      </c>
-      <c r="D85" t="s">
-        <v>41</v>
-      </c>
-      <c r="E85" s="1">
-        <v>36</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/Material.xlsx
+++ b/data/Material.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\orcamentos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83FF54AC-74B4-444F-9B86-88B562D354CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460771A4-27CB-4E1A-A646-15F6508A3225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
   </bookViews>
@@ -235,7 +235,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F84" totalsRowShown="0">
-  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
+  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Mix Acab."/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3E150EE4-3582-4146-8DCA-704614BB6D6C}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{02D0EF72-3F92-4729-A04E-D1B299B7E2C7}" name="Und"/>
@@ -596,7 +602,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -616,7 +622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -636,7 +642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -656,7 +662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -676,7 +682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -696,7 +702,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -716,7 +722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -736,7 +742,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -756,7 +762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -776,7 +782,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -796,7 +802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -816,7 +822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -836,7 +842,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -856,7 +862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -876,7 +882,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -896,7 +902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -916,7 +922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -936,7 +942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -956,7 +962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -976,7 +982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -996,7 +1002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -1096,7 +1102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1156,7 +1162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -1176,7 +1182,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -1216,7 +1222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1236,7 +1242,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1256,7 +1262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1276,7 +1282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1296,7 +1302,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1376,7 +1382,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -1396,7 +1402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -1416,7 +1422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1</v>
       </c>
@@ -1436,7 +1442,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -1456,7 +1462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -1476,7 +1482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1516,7 +1522,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -1556,7 +1562,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -1576,7 +1582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -1596,7 +1602,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -1616,7 +1622,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -1636,7 +1642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1656,7 +1662,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -1930,7 +1936,7 @@
         <v>30</v>
       </c>
       <c r="E68" s="1">
-        <v>119.9</v>
+        <v>359.9</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>18</v>
@@ -2036,7 +2042,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -2056,7 +2062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -2076,7 +2082,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -2096,7 +2102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -2116,7 +2122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -2136,7 +2142,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>26</v>
       </c>
@@ -2156,7 +2162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -2176,7 +2182,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>3</v>
       </c>
@@ -2196,7 +2202,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2216,7 +2222,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -2236,7 +2242,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>20</v>
       </c>

--- a/data/Material.xlsx
+++ b/data/Material.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\orcamentos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460771A4-27CB-4E1A-A646-15F6508A3225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A055257-13D7-44B1-B6B1-897F7F6427C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="6" r:id="rId1"/>
@@ -235,13 +235,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F84" totalsRowShown="0">
-  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Mix Acab."/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3E150EE4-3582-4146-8DCA-704614BB6D6C}" name="Descrição"/>
     <tableColumn id="2" xr3:uid="{02D0EF72-3F92-4729-A04E-D1B299B7E2C7}" name="Und"/>
@@ -602,7 +596,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -622,7 +616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -642,7 +636,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -662,7 +656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -682,7 +676,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -702,7 +696,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -722,7 +716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -742,7 +736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -762,7 +756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -782,7 +776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -802,7 +796,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -822,7 +816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -842,7 +836,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -862,7 +856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -882,7 +876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -902,7 +896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -922,7 +916,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -942,7 +936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -962,7 +956,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -982,7 +976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1002,7 +996,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1022,7 +1016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1042,7 +1036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -1082,7 +1076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -1102,7 +1096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1122,7 +1116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -1142,7 +1136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1162,7 +1156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -1182,7 +1176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1202,7 +1196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -1222,7 +1216,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1242,7 +1236,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1262,7 +1256,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1282,7 +1276,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1302,7 +1296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1322,7 +1316,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -1342,7 +1336,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1362,7 +1356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1382,7 +1376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -1402,7 +1396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -1422,7 +1416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1</v>
       </c>
@@ -1442,7 +1436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>2</v>
       </c>
@@ -1462,7 +1456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -1482,7 +1476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -1502,7 +1496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1522,7 +1516,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -1542,7 +1536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>26</v>
       </c>
@@ -1562,7 +1556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -1582,7 +1576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -1602,7 +1596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>16</v>
       </c>
@@ -1622,7 +1616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -1642,7 +1636,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1662,7 +1656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -2042,7 +2036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -2062,7 +2056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -2082,7 +2076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -2102,7 +2096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>28</v>
       </c>
@@ -2122,7 +2116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -2142,7 +2136,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>26</v>
       </c>
@@ -2162,7 +2156,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -2182,7 +2176,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>3</v>
       </c>
@@ -2202,7 +2196,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2222,7 +2216,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -2242,7 +2236,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>20</v>
       </c>

--- a/data/Material.xlsx
+++ b/data/Material.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\orcamentos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A055257-13D7-44B1-B6B1-897F7F6427C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C04F810-E41B-47E4-9121-3D293716C1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{0C19E045-9576-446E-B6AC-D848E94AC89E}"/>
   </bookViews>
   <sheets>
     <sheet name="Geral" sheetId="6" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="42">
   <si>
     <t>Arame Recozido</t>
   </si>
@@ -159,6 +160,9 @@
   </si>
   <si>
     <t xml:space="preserve">Intermunicipal </t>
+  </si>
+  <si>
+    <t>Real Spin</t>
   </si>
 </sst>
 </file>
@@ -184,19 +188,69 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -205,20 +259,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="8">
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -234,15 +368,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F84" totalsRowShown="0">
-  <autoFilter ref="A1:F84" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}" name="Tabela13" displayName="Tabela13" ref="A1:F102" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:F102" xr:uid="{A995F586-721C-4E7D-8976-2A798AC81BB2}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3E150EE4-3582-4146-8DCA-704614BB6D6C}" name="Descrição"/>
-    <tableColumn id="2" xr3:uid="{02D0EF72-3F92-4729-A04E-D1B299B7E2C7}" name="Und"/>
-    <tableColumn id="3" xr3:uid="{E35A1F86-B51A-4135-8455-367B6BAD66B5}" name="Qnt" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{7CCF3AC5-2546-4A38-95A6-E04EC688DC34}" name="Local"/>
-    <tableColumn id="5" xr3:uid="{0B1806D1-FED9-4573-88BD-38E411D4DB9B}" name="Valor Un" dataCellStyle="Moeda"/>
-    <tableColumn id="6" xr3:uid="{8EA2C009-E0CF-4C5C-B650-ACF37974B7E2}" name="Categoria" dataCellStyle="Moeda"/>
+    <tableColumn id="1" xr3:uid="{3E150EE4-3582-4146-8DCA-704614BB6D6C}" name="Descrição" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{02D0EF72-3F92-4729-A04E-D1B299B7E2C7}" name="Und" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{E35A1F86-B51A-4135-8455-367B6BAD66B5}" name="Qnt" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{7CCF3AC5-2546-4A38-95A6-E04EC688DC34}" name="Local" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{0B1806D1-FED9-4573-88BD-38E411D4DB9B}" name="Valor Un" dataDxfId="3" dataCellStyle="Moeda"/>
+    <tableColumn id="6" xr3:uid="{8EA2C009-E0CF-4C5C-B650-ACF37974B7E2}" name="Categoria" dataDxfId="2" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -565,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC58E5CE-1F21-4ED3-80F8-66E615B00334}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
@@ -577,1682 +711,2042 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="10">
         <v>48</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="11">
         <v>62.25</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="10">
         <v>62</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="11">
         <v>40.6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="10">
         <v>80</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="11">
         <v>13.5</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="10">
+        <v>10</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="11">
         <v>36.6</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="10">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="11">
         <v>20</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="10">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="11">
         <v>19</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="10">
+        <v>18</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="11">
         <v>19</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="B9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="10">
         <v>6800</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="11">
         <v>1.51</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2">
+      <c r="B10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="10">
         <v>80</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="11">
         <v>32.799999999999997</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="10">
         <v>60</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="11">
         <v>24.5</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10">
         <v>20</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="11">
         <v>20.7</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="10">
         <v>2</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="11">
         <v>190</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="B14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="10">
         <v>1</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="11">
         <v>290</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="10">
         <v>165</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="11">
         <v>50</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="10">
         <v>100</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="11">
         <v>19.2</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="10">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="11">
         <v>170</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="10">
         <v>12</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="11">
         <v>156</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="10">
         <v>14</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="11">
         <v>190</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="10">
         <v>48</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="11">
         <v>88</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="10">
         <v>62</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="11">
         <v>51.59</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="10">
         <v>80</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="11">
         <v>16.5</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="2">
-        <v>10</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C23" s="10">
+        <v>10</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="11">
         <v>52.69</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="10">
         <v>50</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="11">
         <v>23.65</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="10">
         <v>25</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="11">
         <v>26.29</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="2">
-        <v>18</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C26" s="10">
+        <v>18</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="11">
         <v>26.29</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="10">
         <v>6800</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="11">
         <v>0.95</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="10">
         <v>80</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="11">
         <v>51.4</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="10">
         <v>60</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="11">
         <v>39.71</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2">
+      <c r="B30" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="10">
         <v>20</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="11">
         <v>20.9</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2">
+      <c r="B31" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="10">
         <v>2</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="11">
         <v>315</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="B32" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="10">
         <v>1</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="11">
         <v>439.45</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="10">
         <v>165</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="11">
         <v>60.4</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="10">
         <v>100</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="11">
         <v>24.2</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="10">
         <v>16</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="11">
         <v>185</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="10">
         <v>12</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="11">
         <v>165</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="10">
         <v>14</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="11">
         <v>198</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="10">
         <v>48</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="11">
         <v>63</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="10">
         <v>62</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="11">
         <v>43</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="10">
         <v>80</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="11">
         <v>14</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="2">
-        <v>10</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C41" s="10">
+        <v>10</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="11">
         <v>52</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="10">
         <v>50</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="11">
         <v>19.899999999999999</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="10">
         <v>25</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="11">
         <v>19.899999999999999</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="2">
-        <v>18</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C44" s="10">
+        <v>18</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="11">
         <v>19.899999999999999</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2">
+      <c r="B45" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="10">
         <v>6800</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="11">
         <v>1.3</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B46" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="2">
+      <c r="B46" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="10">
         <v>80</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="11">
         <v>39.9</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2">
+      <c r="B47" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="10">
         <v>60</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="11">
         <v>34</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="2">
+      <c r="B48" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="10">
         <v>20</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="11">
         <v>19.899999999999999</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B49" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="B49" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="10">
         <v>2</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="11">
         <v>179</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="2">
+      <c r="B50" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="10">
         <v>1</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="11">
         <v>329</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="10">
         <v>165</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="11">
         <v>55.5</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="10">
         <v>100</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="11">
         <v>18.899999999999999</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="10">
         <v>16</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="11">
         <v>159</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="10">
         <v>12</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="11">
         <v>140</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="A55" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="10">
         <v>14</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="11">
         <v>159</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="A56" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="10">
         <v>48</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="11">
         <v>69.900000000000006</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="A57" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="10">
         <v>62</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="11">
         <v>49.9</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="A58" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="10">
         <v>80</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="11">
         <v>15.9</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="2">
-        <v>10</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C59" s="10">
+        <v>10</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="11">
         <v>39.9</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="10">
         <v>50</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="11">
         <v>18.899999999999999</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="10">
         <v>25</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="11">
         <v>18.899999999999999</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="2">
-        <v>18</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="C62" s="10">
+        <v>18</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="11">
         <v>18.899999999999999</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="2">
+      <c r="B63" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="10">
         <v>6800</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="11">
         <v>1.35</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" s="2">
+      <c r="B64" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="10">
         <v>80</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="11">
         <v>39.9</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B65" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="2">
+      <c r="B65" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="10">
         <v>60</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="11">
         <v>32.9</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="2">
+      <c r="B66" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="10">
         <v>20</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="11">
         <v>19</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B67" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" s="2">
+      <c r="B67" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="10">
         <v>2</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="11">
         <v>359.9</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B68" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="2">
+      <c r="B68" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="10">
         <v>1</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="11">
         <v>359.9</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="10">
         <v>165</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="11">
         <v>48.9</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C70" s="2">
+      <c r="C70" s="10">
         <v>100</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="11">
         <v>18.5</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="2">
+      <c r="C71" s="10">
         <v>16</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="11">
         <v>170</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C72" s="2">
+      <c r="C72" s="10">
         <v>12</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="11">
         <v>155</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="2">
+      <c r="C73" s="10">
         <v>14</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="11">
         <v>185</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C74" s="2">
+      <c r="C74" s="10">
         <v>48</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="11">
         <v>54.5</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="2">
+      <c r="C75" s="10">
         <v>62</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="11">
         <v>36.5</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="10">
         <v>80</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="11">
         <v>11</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C77" s="2">
-        <v>10</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="C77" s="10">
+        <v>10</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77" s="11">
         <v>46</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="11" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B78" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="2">
+      <c r="B78" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="10">
         <v>6800</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78" s="11">
         <v>1.18</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B79" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="2">
+      <c r="B79" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="10">
         <v>2</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79" s="11">
         <v>188.87</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="2">
+      <c r="B80" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="10">
         <v>1</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E80" s="11">
         <v>283</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C81" s="2">
+      <c r="C81" s="10">
         <v>16</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81" s="11">
         <v>110</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C82" s="2">
+      <c r="C82" s="10">
         <v>12</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82" s="11">
         <v>110</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="10">
         <v>14</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83" s="11">
         <v>118</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="2">
+      <c r="B84" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="10">
         <v>6800</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84" s="11">
         <v>1</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="14">
+        <v>48</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85" s="11">
+        <v>62</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="14">
+        <v>62</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E86" s="11">
+        <v>42</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="14">
+        <v>80</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" s="11">
+        <v>17</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="14">
+        <v>10</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88" s="11">
+        <v>39</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="14">
+        <v>50</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" s="11">
+        <v>22.68</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="14">
+        <v>25</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" s="11">
+        <v>23</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="14">
+        <v>18</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="11">
+        <v>23</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="14">
+        <v>6800</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="14">
+        <v>80</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" s="11">
+        <v>42</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="14">
+        <v>60</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94" s="11">
+        <v>36</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="14">
+        <v>20</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="11">
+        <v>20</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="14">
+        <v>2</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96" s="11">
+        <v>324</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="14">
+        <v>1</v>
+      </c>
+      <c r="D97" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97" s="11">
+        <v>500</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" s="14">
+        <v>165</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98" s="11">
+        <v>38.9</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="14">
+        <v>100</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E99" s="11">
+        <v>20</v>
+      </c>
+      <c r="F99" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" s="14">
+        <v>16</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" s="11">
+        <v>189</v>
+      </c>
+      <c r="F100" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" s="14">
+        <v>12</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" s="11">
+        <v>155</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" s="17">
+        <v>14</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102" s="18">
+        <v>189</v>
+      </c>
+      <c r="F102" s="11" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2263,4 +2757,324 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1BC48E-B7F9-46AB-A2AC-C8B9048E4AF2}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="7">
+        <v>48</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8">
+        <v>62</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7">
+        <v>80</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="1">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="8">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8">
+        <v>6800</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7">
+        <v>80</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>60</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7">
+        <v>20</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8">
+        <v>165</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="1">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7">
+        <v>100</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="8">
+        <v>16</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="7">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="8">
+        <v>14</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="1">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>